--- a/src-tauri/tests/fixtures/workbook/formula-function-matrix.xlsx
+++ b/src-tauri/tests/fixtures/workbook/formula-function-matrix.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Formula Matrix" sheetId="1" r:id="rId1"/>
+    <sheet name="Lookup Data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>Value</t>
   </si>
@@ -86,6 +87,81 @@
   </si>
   <si>
     <t>unknown_function</t>
+  </si>
+  <si>
+    <t>conditional_sumif</t>
+  </si>
+  <si>
+    <t>conditional_countif</t>
+  </si>
+  <si>
+    <t>conditional_averageif</t>
+  </si>
+  <si>
+    <t>conditional_wildcard</t>
+  </si>
+  <si>
+    <t>lookup_vlookup_exact</t>
+  </si>
+  <si>
+    <t>lookup_vlookup_approximate</t>
+  </si>
+  <si>
+    <t>lookup_hlookup_exact</t>
+  </si>
+  <si>
+    <t>lookup_index</t>
+  </si>
+  <si>
+    <t>lookup_match_exact</t>
+  </si>
+  <si>
+    <t>lookup_match_approximate</t>
+  </si>
+  <si>
+    <t>lookup_text_result</t>
+  </si>
+  <si>
+    <t>lookup_not_found</t>
+  </si>
+  <si>
+    <t>lookup_error_recovery</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Starter</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Pro</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Enterprise</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -426,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
@@ -625,6 +701,233 @@
         <v>#NAME?</v>
       </c>
     </row>
+    <row r="20" spans="4:5">
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20">
+        <f>SUMIF(A2:A4,"&gt;15")</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5">
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21">
+        <f>COUNTIF(A2:A4,"&gt;=20")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5">
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22">
+        <f>AVERAGEIF(A2:A4,"&gt;10")</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5">
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23">
+        <f>COUNTIF('Lookup Data'!A2:A6,"?")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5">
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24">
+        <f>VLOOKUP("B",'Lookup Data'!A2:B6,2,FALSE)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5">
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" t="str">
+        <f>VLOOKUP(25,'Lookup Data'!E2:F5,2,TRUE)</f>
+        <v>Pro</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5">
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26">
+        <f>HLOOKUP("C",'Lookup Data'!A8:D9,2,FALSE)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5">
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27">
+        <f>INDEX('Lookup Data'!B2:B6,3)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5">
+      <c r="D28" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28">
+        <f>MATCH("C",'Lookup Data'!A2:A6,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5">
+      <c r="D29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29">
+        <f>MATCH(25,'Lookup Data'!E2:E5,1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5">
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30">
+        <f>VLOOKUP("D",'Lookup Data'!A2:B6,2,FALSE)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5">
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="e">
+        <f>VLOOKUP("Z",'Lookup Data'!A2:B6,2,FALSE)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5">
+      <c r="D32" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" t="str">
+        <f>IFERROR(E31,"missing")</f>
+        <v>missing</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3">
+        <v>200</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4">
+        <v>300</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>100</v>
+      </c>
+      <c r="B9">
+        <v>200</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src-tauri/tests/fixtures/workbook/formula-function-matrix.xlsx
+++ b/src-tauri/tests/fixtures/workbook/formula-function-matrix.xlsx
@@ -14,8 +14,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
   <si>
     <t>Value</t>
   </si>
@@ -23,6 +45,9 @@
     <t>Text</t>
   </si>
   <si>
+    <t>Region</t>
+  </si>
+  <si>
     <t>Case</t>
   </si>
   <si>
@@ -32,12 +57,18 @@
     <t xml:space="preserve"> long edit </t>
   </si>
   <si>
+    <t>West</t>
+  </si>
+  <si>
     <t>aggregate_sum</t>
   </si>
   <si>
     <t>workspace</t>
   </si>
   <si>
+    <t>East</t>
+  </si>
+  <si>
     <t>aggregate_average</t>
   </si>
   <si>
@@ -126,6 +157,81 @@
   </si>
   <si>
     <t>lookup_error_recovery</t>
+  </si>
+  <si>
+    <t>multi_sumifs</t>
+  </si>
+  <si>
+    <t>multi_countifs</t>
+  </si>
+  <si>
+    <t>multi_averageifs</t>
+  </si>
+  <si>
+    <t>multi_no_match</t>
+  </si>
+  <si>
+    <t>date_create</t>
+  </si>
+  <si>
+    <t>date_year</t>
+  </si>
+  <si>
+    <t>date_month</t>
+  </si>
+  <si>
+    <t>date_day</t>
+  </si>
+  <si>
+    <t>date_leap_day</t>
+  </si>
+  <si>
+    <t>date_error_propagation</t>
+  </si>
+  <si>
+    <t>xlookup_exact_number</t>
+  </si>
+  <si>
+    <t>xlookup_text_result</t>
+  </si>
+  <si>
+    <t>xlookup_not_found_fallback</t>
+  </si>
+  <si>
+    <t>xlookup_reverse_search</t>
+  </si>
+  <si>
+    <t>xlookup_wildcard</t>
+  </si>
+  <si>
+    <t>xlookup_next_smaller</t>
+  </si>
+  <si>
+    <t>xlookup_row_vector</t>
+  </si>
+  <si>
+    <t>xlookup_not_found_error</t>
+  </si>
+  <si>
+    <t>xlookup_error_recovery</t>
+  </si>
+  <si>
+    <t>volatile_offset_range</t>
+  </si>
+  <si>
+    <t>volatile_indirect_same_sheet</t>
+  </si>
+  <si>
+    <t>volatile_indirect_cross_sheet</t>
+  </si>
+  <si>
+    <t>volatile_rand_bounds</t>
+  </si>
+  <si>
+    <t>volatile_randbetween_fixed</t>
+  </si>
+  <si>
+    <t>volatile_clock_relation</t>
   </si>
   <si>
     <t>Code</t>
@@ -502,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
@@ -517,11 +623,14 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -529,10 +638,13 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2">
         <f>SUM(A2:A4)</f>
@@ -544,10 +656,13 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3">
         <f>AVERAGE(A2:A4)</f>
@@ -558,8 +673,11 @@
       <c r="A4">
         <v>30</v>
       </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4">
         <f>MIN(A2:A4)</f>
@@ -568,7 +686,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="D5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <f>MAX(A2:A4)</f>
@@ -577,7 +695,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="D6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <f>COUNT(A2:A4)</f>
@@ -586,7 +704,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="D7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <f>ABS(-12.5)</f>
@@ -595,7 +713,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <f>ROUND(12.345,2)</f>
@@ -604,7 +722,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="str">
         <f>IF(A4&gt;25,"high","low")</f>
@@ -613,7 +731,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="D10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E10" t="b">
         <f>AND(A2=10,A4=30)</f>
@@ -622,7 +740,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="D11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E11" t="b">
         <f>OR(A2=0,A3=20)</f>
@@ -631,7 +749,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="D12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E12" t="b">
         <f>NOT(A2=0)</f>
@@ -640,7 +758,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="D13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E13" t="str">
         <f>_xlfn.CONCAT("Long","Edit")</f>
@@ -649,7 +767,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="D14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14">
         <f>LEN(TRIM(B2))</f>
@@ -658,7 +776,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="D15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E15" t="str">
         <f>UPPER(B3)</f>
@@ -667,7 +785,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="D16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" t="e">
         <f>1/0</f>
@@ -676,7 +794,7 @@
     </row>
     <row r="17" spans="4:5">
       <c r="D17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E17" t="e">
         <f>E16+1</f>
@@ -685,7 +803,7 @@
     </row>
     <row r="18" spans="4:5">
       <c r="D18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E18" t="str">
         <f>IFERROR(E16,"recovered")</f>
@@ -694,7 +812,7 @@
     </row>
     <row r="19" spans="4:5">
       <c r="D19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E19" t="e">
         <f>LONGEDIT_UNKNOWN(A2)</f>
@@ -703,7 +821,7 @@
     </row>
     <row r="20" spans="4:5">
       <c r="D20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E20">
         <f>SUMIF(A2:A4,"&gt;15")</f>
@@ -712,7 +830,7 @@
     </row>
     <row r="21" spans="4:5">
       <c r="D21" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E21">
         <f>COUNTIF(A2:A4,"&gt;=20")</f>
@@ -721,7 +839,7 @@
     </row>
     <row r="22" spans="4:5">
       <c r="D22" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E22">
         <f>AVERAGEIF(A2:A4,"&gt;10")</f>
@@ -730,7 +848,7 @@
     </row>
     <row r="23" spans="4:5">
       <c r="D23" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E23">
         <f>COUNTIF('Lookup Data'!A2:A6,"?")</f>
@@ -739,7 +857,7 @@
     </row>
     <row r="24" spans="4:5">
       <c r="D24" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E24">
         <f>VLOOKUP("B",'Lookup Data'!A2:B6,2,FALSE)</f>
@@ -748,7 +866,7 @@
     </row>
     <row r="25" spans="4:5">
       <c r="D25" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E25" t="str">
         <f>VLOOKUP(25,'Lookup Data'!E2:F5,2,TRUE)</f>
@@ -757,7 +875,7 @@
     </row>
     <row r="26" spans="4:5">
       <c r="D26" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E26">
         <f>HLOOKUP("C",'Lookup Data'!A8:D9,2,FALSE)</f>
@@ -766,7 +884,7 @@
     </row>
     <row r="27" spans="4:5">
       <c r="D27" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E27">
         <f>INDEX('Lookup Data'!B2:B6,3)</f>
@@ -775,7 +893,7 @@
     </row>
     <row r="28" spans="4:5">
       <c r="D28" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E28">
         <f>MATCH("C",'Lookup Data'!A2:A6,0)</f>
@@ -784,7 +902,7 @@
     </row>
     <row r="29" spans="4:5">
       <c r="D29" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E29">
         <f>MATCH(25,'Lookup Data'!E2:E5,1)</f>
@@ -793,7 +911,7 @@
     </row>
     <row r="30" spans="4:5">
       <c r="D30" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E30">
         <f>VLOOKUP("D",'Lookup Data'!A2:B6,2,FALSE)</f>
@@ -802,7 +920,7 @@
     </row>
     <row r="31" spans="4:5">
       <c r="D31" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E31" t="e">
         <f>VLOOKUP("Z",'Lookup Data'!A2:B6,2,FALSE)</f>
@@ -811,11 +929,236 @@
     </row>
     <row r="32" spans="4:5">
       <c r="D32" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E32" t="str">
         <f>IFERROR(E31,"missing")</f>
         <v>missing</v>
+      </c>
+    </row>
+    <row r="33" spans="4:5">
+      <c r="D33" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33">
+        <f>SUMIFS(A2:A4,A2:A4,"&gt;=20",C2:C4,"East")</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="4:5">
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34">
+        <f>COUNTIFS(A2:A4,"&gt;10",C2:C4,"East")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="4:5">
+      <c r="D35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35">
+        <f>AVERAGEIFS(A2:A4,C2:C4,"East",A2:A4,"&lt;30")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="4:5">
+      <c r="D36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36">
+        <f>COUNTIFS(A2:A4,"&gt;100",C2:C4,"East")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:5">
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37">
+        <f>DATE(2024,2,29)</f>
+        <v>45351</v>
+      </c>
+    </row>
+    <row r="38" spans="4:5">
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38">
+        <f>YEAR(DATE(2024,2,29))</f>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="39" spans="4:5">
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39">
+        <f>MONTH(DATE(2024,2,29))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="4:5">
+      <c r="D40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40">
+        <f>DAY(DATE(2024,2,29))</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="4:5">
+      <c r="D41" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41">
+        <f>DAY(DATE(2024,3,0))</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="4:5">
+      <c r="D42" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" t="e">
+        <f>YEAR("not-a-date")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="4:5">
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" cm="1">
+        <f t="array" ref="E43">_xlfn.XLOOKUP("B",'Lookup Data'!A2:A6,'Lookup Data'!B2:B6)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="4:5">
+      <c r="D44" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" cm="1">
+        <f t="array" ref="E44">_xlfn.XLOOKUP("D",'Lookup Data'!A2:A6,'Lookup Data'!B2:B6)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="4:5">
+      <c r="D45" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" cm="1" t="str">
+        <f t="array" ref="E45">_xlfn.XLOOKUP("Z",'Lookup Data'!A2:A6,'Lookup Data'!B2:B6,"missing")</f>
+        <v>missing</v>
+      </c>
+    </row>
+    <row r="46" spans="4:5">
+      <c r="D46" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" cm="1">
+        <f t="array" ref="E46">_xlfn.XLOOKUP("East",C2:C4,A2:A4,,0,-1)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="4:5">
+      <c r="D47" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" cm="1">
+        <f t="array" ref="E47">_xlfn.XLOOKUP("C*",'Lookup Data'!A2:A6,'Lookup Data'!B2:B6,,2)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="48" spans="4:5">
+      <c r="D48" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" cm="1" t="str">
+        <f t="array" ref="E48">_xlfn.XLOOKUP(25,'Lookup Data'!E2:E5,'Lookup Data'!F2:F5,,-1)</f>
+        <v>Pro</v>
+      </c>
+    </row>
+    <row r="49" spans="4:5">
+      <c r="D49" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" cm="1">
+        <f t="array" ref="E49">_xlfn.XLOOKUP("C",'Lookup Data'!A8:D8,'Lookup Data'!A9:D9)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="50" spans="4:5">
+      <c r="D50" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" cm="1" t="e">
+        <f t="array" ref="E50">_xlfn.XLOOKUP("Z",'Lookup Data'!A2:A6,'Lookup Data'!B2:B6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="4:5">
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" t="str">
+        <f>IFERROR(E50,"recovered")</f>
+        <v>recovered</v>
+      </c>
+    </row>
+    <row r="52" spans="4:5">
+      <c r="D52" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52">
+        <f>SUM(OFFSET(A2,1,0,2,1))</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="4:5">
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53">
+        <f>INDIRECT("A3")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="4:5">
+      <c r="D54" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54">
+        <f>SUM(INDIRECT("'Lookup Data'!B4"))</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" spans="4:5">
+      <c r="D55" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" t="b">
+        <f>AND(RAND()&gt;=0,RAND()&lt;1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="4:5">
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56">
+        <f>RANDBETWEEN(5,5)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="4:5">
+      <c r="D57" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" t="b">
+        <f>AND(TODAY()&lt;=NOW(),NOW()&lt;TODAY()+1)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -830,15 +1173,15 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -847,12 +1190,12 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="B3">
         <v>200</v>
@@ -861,12 +1204,12 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>300</v>
@@ -875,26 +1218,26 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="E5">
         <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B6">
         <v>500</v>
@@ -902,16 +1245,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:6">

--- a/src-tauri/tests/fixtures/workbook/formula-function-matrix.xlsx
+++ b/src-tauri/tests/fixtures/workbook/formula-function-matrix.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="85">
   <si>
     <t>Value</t>
   </si>
@@ -232,6 +232,30 @@
   </si>
   <si>
     <t>volatile_clock_relation</t>
+  </si>
+  <si>
+    <t>xmatch_exact</t>
+  </si>
+  <si>
+    <t>xmatch_reverse_search</t>
+  </si>
+  <si>
+    <t>xmatch_wildcard</t>
+  </si>
+  <si>
+    <t>xmatch_next_smaller</t>
+  </si>
+  <si>
+    <t>xmatch_next_larger</t>
+  </si>
+  <si>
+    <t>xmatch_row_vector</t>
+  </si>
+  <si>
+    <t>xmatch_not_found</t>
+  </si>
+  <si>
+    <t>xmatch_error_recovery</t>
   </si>
   <si>
     <t>Code</t>
@@ -608,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
@@ -1159,6 +1183,78 @@
       <c r="E57" t="b">
         <f>AND(TODAY()&lt;=NOW(),NOW()&lt;TODAY()+1)</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="4:5">
+      <c r="D58" t="s">
+        <v>65</v>
+      </c>
+      <c r="E58">
+        <f>_xlfn.XMATCH("C",'Lookup Data'!A2:A6)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:5">
+      <c r="D59" t="s">
+        <v>66</v>
+      </c>
+      <c r="E59">
+        <f>_xlfn.XMATCH("East",C2:C4,0,-1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:5">
+      <c r="D60" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60">
+        <f>_xlfn.XMATCH("C*",'Lookup Data'!A2:A6,2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="4:5">
+      <c r="D61" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61">
+        <f>_xlfn.XMATCH(25,'Lookup Data'!E2:E5,-1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="4:5">
+      <c r="D62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62">
+        <f>_xlfn.XMATCH(25,'Lookup Data'!E2:E5,1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="4:5">
+      <c r="D63" t="s">
+        <v>70</v>
+      </c>
+      <c r="E63">
+        <f>_xlfn.XMATCH("C",'Lookup Data'!A8:D8)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="4:5">
+      <c r="D64" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" t="e">
+        <f>_xlfn.XMATCH("Z",'Lookup Data'!A2:A6)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="4:5">
+      <c r="D65" t="s">
+        <v>72</v>
+      </c>
+      <c r="E65" t="str">
+        <f>IFERROR(E64,"recovered")</f>
+        <v>recovered</v>
       </c>
     </row>
   </sheetData>
@@ -1173,15 +1269,15 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -1190,12 +1286,12 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B3">
         <v>200</v>
@@ -1204,12 +1300,12 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>300</v>
@@ -1218,26 +1314,26 @@
         <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E5">
         <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B6">
         <v>500</v>
@@ -1245,16 +1341,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:6">
